--- a/Inhalt/Zustandsautomat_NGHR.xlsx
+++ b/Inhalt/Zustandsautomat_NGHR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I767888/Desktop/se2-nghr-gruppe4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I767888/Desktop/se2-nghr-gruppe4/Inhalt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1BECE5-82E1-3D48-A909-5C55ABE1490C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B75E067F-822E-4B4B-8BBC-0E456A39C0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="137">
   <si>
     <t>ID</t>
   </si>
@@ -382,6 +382,57 @@
   </si>
   <si>
     <t>Eine ausländische Tochtergesellschaft ist eine rechtlich selbstständige Niederlassung der Sonnenschein AG im Ausland, die für entsendete Mitarbeiter die Gehaltszahlung übernimmt.</t>
+  </si>
+  <si>
+    <t>Mitarbeiterstatus</t>
+  </si>
+  <si>
+    <t>Der Mitarbeiterstatus ist eine Eigenschaft eines Mitarbeiters, die seine aktuelle Stellung im Lebenszyklus des Arbeitsverhältnisses angibt.</t>
+  </si>
+  <si>
+    <t>angelegt</t>
+  </si>
+  <si>
+    <t>Angelegt ist ein Mitarbeiter, dessen Arbeitsvertrag geschlossen, dessen Vertragsbeginn aber noch nicht erreicht ist.</t>
+  </si>
+  <si>
+    <t>aktiv</t>
+  </si>
+  <si>
+    <t>Aktiv ist ein Mitarbeiter, dessen Arbeitsverhältnis läuft und für dessen Gehaltszahlung die Sonnenschein AG selbst (nicht etwa eine ausländische Tochtergesellschaft) aufkommt.</t>
+  </si>
+  <si>
+    <t>inaktiv</t>
+  </si>
+  <si>
+    <t>Inaktiv ist ein Mitarbeiter, dessen Arbeitsverhältnis besteht, aber vorübergehend ruht.</t>
+  </si>
+  <si>
+    <t>entsendet</t>
+  </si>
+  <si>
+    <t>Entsendet ist ein Mitarbeiter mit gültigem Arbeitsvertrag in Deutschland, der befristet ins Ausland entsendet ist und dessen Gehalt währenddessen von einer ausländischen Tochtergesellschaft gezahlt wird.</t>
+  </si>
+  <si>
+    <t>ehemalig</t>
+  </si>
+  <si>
+    <t>Ehemalig ist ein Mitarbeiter, dessen Arbeitsverhältnis beendet ist.</t>
+  </si>
+  <si>
+    <t>Rentner</t>
+  </si>
+  <si>
+    <t>Rentner ist ein ehemaliger Mitarbeiter, der in den Ruhestand getreten ist.</t>
+  </si>
+  <si>
+    <t>Verstorbener ist ein Mitarbeiter, dessen Ableben der Sonnenschein AG bekannt ist.</t>
+  </si>
+  <si>
+    <t>gelöscht</t>
+  </si>
+  <si>
+    <t>Gelöscht ist ein Mitarbeiter, dessen Personenbezogene Daten nicht mehr im System vorhanden sind.</t>
   </si>
 </sst>
 </file>
@@ -531,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -582,6 +633,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1399,94 +1459,116 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1417D2-D9DE-7141-80A2-84170EE58AC1}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="178" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="158.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>84</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+    </row>
+    <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>86</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="19"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>88</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>90</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D4" s="19"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>92</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
         <v>94</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
         <v>96</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="19"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>98</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="19"/>
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>100</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="19"/>
+      <c r="E9" s="20"/>
+    </row>
+    <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>102</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="19"/>
+      <c r="E10" s="20"/>
+    </row>
+    <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
         <v>104</v>
       </c>
@@ -1494,7 +1576,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
         <v>106</v>
       </c>
@@ -1502,7 +1584,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>108</v>
       </c>
@@ -1510,7 +1592,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>110</v>
       </c>
@@ -1518,7 +1600,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>112</v>
       </c>
@@ -1526,7 +1608,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>114</v>
       </c>
@@ -1548,6 +1630,86 @@
       </c>
       <c r="B18" s="15" t="s">
         <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Inhalt/Zustandsautomat_NGHR.xlsx
+++ b/Inhalt/Zustandsautomat_NGHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I767888/Desktop/se2-nghr-gruppe4/Inhalt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B75E067F-822E-4B4B-8BBC-0E456A39C0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECF010A-BBBA-2A48-A07A-6D5E9DD39B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -593,55 +593,55 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1032,13 +1032,13 @@
       <c r="F3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="17" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1058,9 +1058,9 @@
       <c r="F4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
@@ -1078,13 +1078,13 @@
       <c r="F5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="19" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1104,9 +1104,9 @@
       <c r="F6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
     </row>
     <row r="7" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -1172,7 +1172,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1186,7 +1186,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1200,7 +1200,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1214,7 +1214,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1228,7 +1228,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1242,7 +1242,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1256,7 +1256,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1270,7 +1270,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1284,7 +1284,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1298,7 +1298,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1312,7 +1312,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="8" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1326,7 +1326,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1340,7 +1340,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1354,7 +1354,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1368,7 +1368,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1382,35 +1382,35 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1424,30 +1424,30 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1469,246 +1469,250 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="20"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="20"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="20"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="20"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="11" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="13" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="11" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="13" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="11" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="13" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="11" t="s">
         <v>119</v>
       </c>
     </row>
+    <row r="19" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
     <row r="20" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+    </row>
+    <row r="21" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B21" s="9" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>121</v>
-      </c>
-    </row>
     <row r="22" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="13" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="11" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="13" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="11" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="11" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="13" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="11" t="s">
         <v>136</v>
       </c>
     </row>

--- a/Inhalt/Zustandsautomat_NGHR.xlsx
+++ b/Inhalt/Zustandsautomat_NGHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I767888/Desktop/se2-nghr-gruppe4/Inhalt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECF010A-BBBA-2A48-A07A-6D5E9DD39B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCA5E77-CE1D-1D49-8B4E-62CA5739CA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="136">
   <si>
     <t>ID</t>
   </si>
@@ -271,9 +271,6 @@
   </si>
   <si>
     <t>Mitarbeiter zieht zurück nach Deutschland, um wieder direkt bei der Sonnenschein AG zu arbeiten</t>
-  </si>
-  <si>
-    <t>Er</t>
   </si>
   <si>
     <t>Begriff</t>
@@ -1140,11 +1137,6 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="I16" t="s">
-        <v>83</v>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="6">
@@ -1463,181 +1455,181 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="178" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.33203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="158.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="D1" s="14"/>
       <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>88</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>89</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>91</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>92</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>93</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>94</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>95</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>97</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>100</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>101</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>102</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>103</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="16"/>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>104</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>108</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>116</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>120</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -1649,55 +1641,55 @@
         <v>48</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>122</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>126</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -1705,15 +1697,15 @@
         <v>45</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>135</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Inhalt/Zustandsautomat_NGHR.xlsx
+++ b/Inhalt/Zustandsautomat_NGHR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I767888/Desktop/se2-nghr-gruppe4/Inhalt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCA5E77-CE1D-1D49-8B4E-62CA5739CA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E7AA63-4C87-F54F-BE92-3E2CFF290797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aktion" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="123">
   <si>
     <t>ID</t>
   </si>
@@ -51,9 +51,6 @@
     <t>E2</t>
   </si>
   <si>
-    <t>Der Vertragsbeginn des Arbeitsverhältnisses ist das heutige Datum</t>
-  </si>
-  <si>
     <t>Aktiv</t>
   </si>
   <si>
@@ -114,24 +111,15 @@
     <t>E12</t>
   </si>
   <si>
-    <t>Mitarbeiter hat gekündigt und Kündigungsdatum ist heute</t>
-  </si>
-  <si>
     <t>Ehemalig</t>
   </si>
   <si>
     <t>E13</t>
   </si>
   <si>
-    <t>Mitarbeiter wurde gekündigt und Kündigungsdatum ist heute</t>
-  </si>
-  <si>
     <t>E14</t>
   </si>
   <si>
-    <t>Enddatum des Arbeitsverhältnisses im Auflösungsvertrag ist heute</t>
-  </si>
-  <si>
     <t>E15</t>
   </si>
   <si>
@@ -150,21 +138,12 @@
     <t>Gelöscht</t>
   </si>
   <si>
-    <t>E17</t>
-  </si>
-  <si>
     <t>Über das Ableben einer Person wird die Sonnenschein AG informiert</t>
   </si>
   <si>
-    <t>Jeder Zustand</t>
-  </si>
-  <si>
     <t>Verstorben</t>
   </si>
   <si>
-    <t>E18</t>
-  </si>
-  <si>
     <t>Differenz des Ablebedatums und heute ist ≥ 5 Jahre</t>
   </si>
   <si>
@@ -192,9 +171,6 @@
     <t>A3</t>
   </si>
   <si>
-    <t>Neue eindeutige Personalnummer vergeben</t>
-  </si>
-  <si>
     <t>A4</t>
   </si>
   <si>
@@ -243,12 +219,6 @@
     <t>A2, A3, A4</t>
   </si>
   <si>
-    <t>A5, A6</t>
-  </si>
-  <si>
-    <t>Aktiv, inaktiv, entsendet</t>
-  </si>
-  <si>
     <t>Mitarbeiter beginnt ein Sabbatical</t>
   </si>
   <si>
@@ -258,18 +228,6 @@
     <t>Aktiv, Inaktiv, Entsendet</t>
   </si>
   <si>
-    <t>Ehemaliger Mitarbeiter tritt in den Ruhestand</t>
-  </si>
-  <si>
-    <t>Jeder Zustand, außer Gelöscht</t>
-  </si>
-  <si>
-    <t>E19</t>
-  </si>
-  <si>
-    <t>Ehemalig, Inaktiv, Entsendet, Rente, Verstorben</t>
-  </si>
-  <si>
     <t>Mitarbeiter zieht zurück nach Deutschland, um wieder direkt bei der Sonnenschein AG zu arbeiten</t>
   </si>
   <si>
@@ -315,12 +273,6 @@
     <t>Der Vertragsbeginn ist das im Arbeitsvertrag festgelegte Datum, ab dem das Arbeitsverhältnis aktiv wird.</t>
   </si>
   <si>
-    <t>Kündigungsdatum</t>
-  </si>
-  <si>
-    <t>Das Kündigungsdatum ist das im Arbeitsvertrag oder in der Kündigung festgelegte Datum, an dem das Arbeitsverhältnis endet.</t>
-  </si>
-  <si>
     <t>Auflösungsvertrag</t>
   </si>
   <si>
@@ -342,9 +294,6 @@
     <t>ERP-System</t>
   </si>
   <si>
-    <t>Das ERP-System ist ein unternehmensweites IT-System der Sonnenschein AG, das für Controlling, Buchhaltung und Kostenstellenverwaltung zuständig ist und bei Zustandswechseln eines Mitarbeiters von NGHR benachrichtigt wird.</t>
-  </si>
-  <si>
     <t>I&amp;B (Identität und Berechtigungen)</t>
   </si>
   <si>
@@ -387,56 +336,84 @@
     <t>Der Mitarbeiterstatus ist eine Eigenschaft eines Mitarbeiters, die seine aktuelle Stellung im Lebenszyklus des Arbeitsverhältnisses angibt.</t>
   </si>
   <si>
-    <t>angelegt</t>
-  </si>
-  <si>
     <t>Angelegt ist ein Mitarbeiter, dessen Arbeitsvertrag geschlossen, dessen Vertragsbeginn aber noch nicht erreicht ist.</t>
   </si>
   <si>
-    <t>aktiv</t>
-  </si>
-  <si>
     <t>Aktiv ist ein Mitarbeiter, dessen Arbeitsverhältnis läuft und für dessen Gehaltszahlung die Sonnenschein AG selbst (nicht etwa eine ausländische Tochtergesellschaft) aufkommt.</t>
   </si>
   <si>
-    <t>inaktiv</t>
-  </si>
-  <si>
     <t>Inaktiv ist ein Mitarbeiter, dessen Arbeitsverhältnis besteht, aber vorübergehend ruht.</t>
   </si>
   <si>
-    <t>entsendet</t>
-  </si>
-  <si>
     <t>Entsendet ist ein Mitarbeiter mit gültigem Arbeitsvertrag in Deutschland, der befristet ins Ausland entsendet ist und dessen Gehalt währenddessen von einer ausländischen Tochtergesellschaft gezahlt wird.</t>
   </si>
   <si>
-    <t>ehemalig</t>
-  </si>
-  <si>
     <t>Ehemalig ist ein Mitarbeiter, dessen Arbeitsverhältnis beendet ist.</t>
   </si>
   <si>
     <t>Rentner</t>
   </si>
   <si>
-    <t>Rentner ist ein ehemaliger Mitarbeiter, der in den Ruhestand getreten ist.</t>
-  </si>
-  <si>
     <t>Verstorbener ist ein Mitarbeiter, dessen Ableben der Sonnenschein AG bekannt ist.</t>
   </si>
   <si>
-    <t>gelöscht</t>
-  </si>
-  <si>
     <t>Gelöscht ist ein Mitarbeiter, dessen Personenbezogene Daten nicht mehr im System vorhanden sind.</t>
+  </si>
+  <si>
+    <t>Das ERP-System ist ein unternehmensweites IT-System der Sonnenschein AG, das für Controlling, Buchhaltung und Kostenstellenverwaltung zuständig ist.</t>
+  </si>
+  <si>
+    <t>Rentner ist ein Mitarbeiter oder ehemaliger Mitarbeiter, der in den Ruhestand getreten ist.</t>
+  </si>
+  <si>
+    <t>Der Vertragsbeginn des Arbeitsverhältnisses ist kleiner als oder gleich gleich dem heutigen Datum</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Neue eindeutige</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Personalnummer vergeben</t>
+    </r>
+  </si>
+  <si>
+    <t>Jeder Zustandswechsel</t>
+  </si>
+  <si>
+    <t>Ehemalig, Rente</t>
+  </si>
+  <si>
+    <t>Terminierung des Arbeitsverhältnisses</t>
+  </si>
+  <si>
+    <t>Kündigung</t>
+  </si>
+  <si>
+    <t>Eine Kündigung ist eine einseitige Willenserklärung eines Mitarbeiters oder der Sonnenschein AG, die das Enddatum eines Arbeitsvertrags festlegt.</t>
+  </si>
+  <si>
+    <t>Eine Terminierung des Arbeitsverhältnisses ist ein Ereignis, das das Ende eines Arbeitsverhältnisses bewirkt. Eine Terminierung geschieht beim Eintrittsdatum einer Kündung, eines Auflösungsvertrag, Eintritt in den Ruhestand oder am Abledatum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminierung des Arbeitsverhältnisses des Mitarbeiters tritt ein </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,6 +443,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -511,7 +494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -575,11 +558,117 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -629,16 +718,49 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -949,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2DDF3D-EB9A-E04A-8438-27CF95FF0BE5}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -961,21 +1083,21 @@
     <col min="10" max="10" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -984,168 +1106,172 @@
         <v>3</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I2" s="18"/>
+      <c r="J2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+    </row>
+    <row r="8" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="9" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    </row>
+    <row r="10" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-    </row>
-    <row r="7" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I15" s="21"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="25"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I16" s="22"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="26"/>
+    </row>
+    <row r="17" spans="9:11" x14ac:dyDescent="0.2">
+      <c r="I17" s="22"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="26"/>
+    </row>
+    <row r="18" spans="9:11" x14ac:dyDescent="0.2">
+      <c r="I18" s="27"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="29"/>
+    </row>
+    <row r="22" spans="9:11" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
+  <mergeCells count="1">
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1196,252 +1322,228 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>31</v>
+      <c r="C14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="D17" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="A18" s="8"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="A19" s="8"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="A20" s="8"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
     </row>
     <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -1462,250 +1564,254 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D1" s="14"/>
       <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
     </row>
     <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="16"/>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="21" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
